--- a/進捗/PlayerAnimation資料.xlsx
+++ b/進捗/PlayerAnimation資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BEE2A7B-34CF-4FF0-8DEB-C0192DBFDB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1C1A4-42BA-4696-B23E-390D23C6B8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="4770" windowWidth="27105" windowHeight="15585" xr2:uid="{343C49A8-A3F0-47E4-BA49-C6872EC960FD}"/>
+    <workbookView xWindow="9615" yWindow="375" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{343C49A8-A3F0-47E4-BA49-C6872EC960FD}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerAnimation" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="424">
   <si>
     <t>Ninja_Acrobatic_Backflip</t>
   </si>
@@ -1922,129 +1922,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>弱攻撃1</t>
-    <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱攻撃2</t>
-    <rPh sb="0" eb="3">
-      <t>ジャクコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱攻撃3</t>
-    <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱攻撃4</t>
-    <rPh sb="0" eb="3">
-      <t>ジャクコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強攻撃1</t>
-    <rPh sb="0" eb="3">
-      <t>キョウコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強攻撃2</t>
-    <rPh sb="0" eb="3">
-      <t>キョウコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中攻撃1</t>
-    <rPh sb="0" eb="4">
-      <t>クウチュウコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中攻撃2</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中攻撃3</t>
-    <rPh sb="0" eb="4">
-      <t>クウチュウコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中攻撃4</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中強攻撃1</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱攻撃5</t>
-    <rPh sb="0" eb="3">
-      <t>ジャクコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Skill攻撃1</t>
-    <rPh sb="5" eb="7">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Skill攻撃2</t>
-    <rPh sb="5" eb="7">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Skill攻撃3</t>
-    <rPh sb="5" eb="7">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>必殺技1</t>
     <rPh sb="0" eb="3">
       <t>ヒッサツワザ</t>
@@ -2059,17 +1936,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2種</t>
-    <rPh sb="1" eb="2">
-      <t>シュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>貧弱すぎる4連攻撃</t>
     <rPh sb="0" eb="2">
       <t>ヒンジャク</t>
@@ -2132,13 +1998,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>忍殺</t>
-    <rPh sb="0" eb="2">
-      <t>ニンサツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>忍殺(空)</t>
     <rPh sb="0" eb="2">
       <t>ニンサツ</t>
@@ -2282,6 +2141,307 @@
   </si>
   <si>
     <t>Ninja_QuickDash_Forward_Loop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AvoidBack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JustAvoidBack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UltAttack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上弱攻撃1</t>
+  </si>
+  <si>
+    <t>地上弱攻撃2</t>
+  </si>
+  <si>
+    <t>地上弱攻撃3</t>
+  </si>
+  <si>
+    <t>地上弱攻撃4</t>
+  </si>
+  <si>
+    <t>地上弱攻撃5</t>
+  </si>
+  <si>
+    <t>#強攻撃</t>
+  </si>
+  <si>
+    <t>地上強攻撃1</t>
+  </si>
+  <si>
+    <t>地上強攻撃2</t>
+  </si>
+  <si>
+    <t>#連携技</t>
+  </si>
+  <si>
+    <t>切り上げ攻撃</t>
+  </si>
+  <si>
+    <t>#空中弱攻撃</t>
+  </si>
+  <si>
+    <t>空中弱攻撃1</t>
+  </si>
+  <si>
+    <t>空中弱攻撃2</t>
+  </si>
+  <si>
+    <t>空中弱攻撃3</t>
+  </si>
+  <si>
+    <t>空中弱攻撃4</t>
+  </si>
+  <si>
+    <t>#空中強攻撃</t>
+  </si>
+  <si>
+    <t>空中強攻撃1</t>
+  </si>
+  <si>
+    <t>ダッシュ攻撃</t>
+  </si>
+  <si>
+    <t>#スキル攻撃</t>
+  </si>
+  <si>
+    <t>スキル弱1</t>
+  </si>
+  <si>
+    <t>スキル弱2</t>
+  </si>
+  <si>
+    <t>スキル弱3</t>
+  </si>
+  <si>
+    <t>忍殺(何パターンかほしい</t>
+    <rPh sb="0" eb="2">
+      <t>ニンサツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁キック</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁走り</t>
+    <rPh sb="0" eb="2">
+      <t>カベバシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_ComboAttack4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_AttackAir1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_AttackUp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_Jump_02_jump</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sword_ParryCounter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絶技あり</t>
+    <rPh sb="0" eb="2">
+      <t>ゼツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗殺あり</t>
+    <rPh sb="0" eb="2">
+      <t>アンサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗殺/絶技あり</t>
+    <rPh sb="0" eb="2">
+      <t>アンサツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_Shufle_Sprint_Forward</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_ComboAttack1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絶技</t>
+    <rPh sb="0" eb="2">
+      <t>ゼツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_Execution</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_Stunding_SwordDrawn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>movie入れるなら歩きとか剣抜くときとか入れる</t>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケンヌ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣閉める</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_idle_Standing_Sheathe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣ぬく</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_idle_Standing_Unsheathe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_Dodge_Forward</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SwordAnim_Dodge_Back</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_acrobat_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hit_F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hit_Air_F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hit_Death</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クナイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_Chudan_Kunai_Throw</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ずっと待機状態用</t>
+    <rPh sb="3" eb="8">
+      <t>タイキジョウタイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ninja_Idle_LoosenUp02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Combo_Attack_Wave_05_03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩き</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Walk_Loop_F_0_RM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中ダッシュ</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Swordman_PowerAttack2つ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2742,7 +2902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A4DCE3-85B0-4450-805A-4CF6BA0E7C5A}">
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="55.625" customWidth="1"/>
@@ -2929,7 +3089,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -2940,7 +3100,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -2951,10 +3111,10 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -2965,7 +3125,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>318</v>
       </c>
@@ -2976,10 +3136,10 @@
         <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -2990,7 +3150,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -3001,7 +3161,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
@@ -3012,7 +3172,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -3023,7 +3183,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
@@ -3034,10 +3194,13 @@
         <v>268</v>
       </c>
       <c r="D25" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+        <v>336</v>
+      </c>
+      <c r="H25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
@@ -3048,7 +3211,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
@@ -3056,13 +3219,13 @@
         <v>259</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="D27" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
@@ -3073,7 +3236,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
         <v>27</v>
       </c>
@@ -3084,10 +3247,13 @@
         <v>270</v>
       </c>
       <c r="D29" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+        <v>339</v>
+      </c>
+      <c r="H29" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
@@ -3098,7 +3264,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
@@ -3109,10 +3275,13 @@
         <v>271</v>
       </c>
       <c r="D31" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+        <v>344</v>
+      </c>
+      <c r="H31" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
         <v>30</v>
       </c>
@@ -3123,7 +3292,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
@@ -3134,7 +3303,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
         <v>32</v>
       </c>
@@ -3145,10 +3314,13 @@
         <v>273</v>
       </c>
       <c r="D34" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+        <v>346</v>
+      </c>
+      <c r="H34" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
         <v>33</v>
       </c>
@@ -3159,9 +3331,9 @@
         <v>257</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>259</v>
@@ -3170,10 +3342,13 @@
         <v>274</v>
       </c>
       <c r="D36" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+        <v>347</v>
+      </c>
+      <c r="H36" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>34</v>
       </c>
@@ -3184,7 +3359,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
         <v>35</v>
       </c>
@@ -3195,10 +3370,10 @@
         <v>275</v>
       </c>
       <c r="D38" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>36</v>
       </c>
@@ -3209,7 +3384,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
         <v>37</v>
       </c>
@@ -3220,7 +3395,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
         <v>38</v>
       </c>
@@ -3231,10 +3406,10 @@
         <v>275</v>
       </c>
       <c r="D41" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -3245,7 +3420,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
         <v>40</v>
       </c>
@@ -3256,7 +3431,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>41</v>
       </c>
@@ -3267,7 +3442,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
         <v>42</v>
       </c>
@@ -3278,7 +3453,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
         <v>43</v>
       </c>
@@ -3289,7 +3464,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
         <v>44</v>
       </c>
@@ -3300,7 +3475,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
         <v>45</v>
       </c>
@@ -3311,7 +3486,7 @@
         <v>278</v>
       </c>
       <c r="D48" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -3358,7 +3533,7 @@
         <v>280</v>
       </c>
       <c r="D52" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -3713,7 +3888,7 @@
         <v>291</v>
       </c>
       <c r="D84" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4188,7 @@
         <v>257</v>
       </c>
       <c r="D111" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -4038,7 +4213,7 @@
         <v>257</v>
       </c>
       <c r="D113" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -4096,7 +4271,7 @@
         <v>297</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -4440,7 +4615,7 @@
         <v>297</v>
       </c>
       <c r="D149" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -4696,7 +4871,7 @@
         <v>291</v>
       </c>
       <c r="D172" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -4712,7 +4887,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A174" s="4" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>255</v>
@@ -5214,7 +5389,7 @@
         <v>312</v>
       </c>
       <c r="D218" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -5578,174 +5753,390 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A0C55C-35BA-4508-B2BD-6769E09ECCF1}">
-  <dimension ref="B2:D45"/>
+  <dimension ref="A2:O63"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
+      <c r="M2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
+      <c r="C3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>323</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
+        <v>398</v>
+      </c>
+      <c r="M4" t="s">
+        <v>404</v>
+      </c>
+      <c r="N4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
+      <c r="M5" t="s">
+        <v>406</v>
+      </c>
+      <c r="N5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>325</v>
       </c>
-      <c r="D6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
+      <c r="C6" t="s">
+        <v>408</v>
+      </c>
+      <c r="M6" t="s">
+        <v>417</v>
+      </c>
+      <c r="O6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C7" t="s">
+        <v>409</v>
+      </c>
+      <c r="M7" t="s">
+        <v>420</v>
+      </c>
+      <c r="N7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
         <v>326</v>
       </c>
-      <c r="C7" t="s">
-        <v>350</v>
-      </c>
-      <c r="D7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
+      <c r="C8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C9" t="s">
+        <v>410</v>
+      </c>
+      <c r="M9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
+      <c r="C11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" t="s">
+        <v>411</v>
+      </c>
+      <c r="D12" t="s">
+        <v>412</v>
+      </c>
+      <c r="E12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C13" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>385</v>
+      </c>
+      <c r="C16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C18" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B19" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>364</v>
+      </c>
+      <c r="B26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B28" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>368</v>
+      </c>
+      <c r="B30" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>369</v>
+      </c>
+      <c r="B31" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>372</v>
+      </c>
+      <c r="B34" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>373</v>
+      </c>
+      <c r="B35" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>375</v>
+      </c>
+      <c r="B37" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>381</v>
+      </c>
+      <c r="B43" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B22" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B23" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
+      <c r="B49" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>415</v>
+      </c>
+      <c r="B51" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>384</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B58" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B59" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B60" s="4" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B32" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B34" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B38" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B40" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B42" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B44" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B45" t="s">
-        <v>360</v>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
